--- a/data_lake/industry/TrendForce/NAND Flash.xlsx
+++ b/data_lake/industry/TrendForce/NAND Flash.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/industry/TrendForce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0609B3B-4093-004C-877C-252A7DA6EFD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D666164E-F996-B140-9BFD-7B019481A16E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17280" yWindow="780" windowWidth="18720" windowHeight="20700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17280" yWindow="780" windowWidth="18720" windowHeight="20700" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Flash" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="393" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="76">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -641,6 +641,9 @@
                 <c:pt idx="31">
                   <c:v>46265</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46272</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -745,6 +748,9 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>4.2850000000000001</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>4.2750000000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -887,6 +893,9 @@
                 <c:pt idx="31">
                   <c:v>46265</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46272</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -991,6 +1000,9 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>3.4449999999999998</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>3.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1133,6 +1145,9 @@
                 <c:pt idx="31">
                   <c:v>46265</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46272</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1237,6 +1252,9 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>37.587000000000003</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>38.587000000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1379,6 +1397,9 @@
                 <c:pt idx="31">
                   <c:v>46265</c:v>
                 </c:pt>
+                <c:pt idx="32">
+                  <c:v>46272</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1483,6 +1504,9 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>18.437999999999999</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>18.638000000000002</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1877,6 +1901,9 @@
                 <c:pt idx="41">
                   <c:v>46265</c:v>
                 </c:pt>
+                <c:pt idx="42">
+                  <c:v>46272</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2011,6 +2038,9 @@
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>20.896000000000001</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>20.707999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2183,6 +2213,9 @@
                 <c:pt idx="41">
                   <c:v>46265</c:v>
                 </c:pt>
+                <c:pt idx="42">
+                  <c:v>46272</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2316,6 +2349,9 @@
                   <c:v>15.923</c:v>
                 </c:pt>
                 <c:pt idx="41">
+                  <c:v>16.808</c:v>
+                </c:pt>
+                <c:pt idx="42">
                   <c:v>16.808</c:v>
                 </c:pt>
               </c:numCache>
@@ -2489,6 +2525,9 @@
                 <c:pt idx="41">
                   <c:v>46265</c:v>
                 </c:pt>
+                <c:pt idx="42">
+                  <c:v>46272</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2622,6 +2661,9 @@
                   <c:v>9.6329999999999991</c:v>
                 </c:pt>
                 <c:pt idx="41">
+                  <c:v>9.9670000000000005</c:v>
+                </c:pt>
+                <c:pt idx="42">
                   <c:v>9.9670000000000005</c:v>
                 </c:pt>
               </c:numCache>
@@ -3017,6 +3059,9 @@
                 <c:pt idx="41">
                   <c:v>46265</c:v>
                 </c:pt>
+                <c:pt idx="42">
+                  <c:v>46272</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3150,6 +3195,9 @@
                   <c:v>2.9649999999999999</c:v>
                 </c:pt>
                 <c:pt idx="41">
+                  <c:v>2.9649999999999999</c:v>
+                </c:pt>
+                <c:pt idx="42">
                   <c:v>2.9649999999999999</c:v>
                 </c:pt>
               </c:numCache>
@@ -3323,6 +3371,9 @@
                 <c:pt idx="41">
                   <c:v>46265</c:v>
                 </c:pt>
+                <c:pt idx="42">
+                  <c:v>46272</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3457,6 +3508,9 @@
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>4.25</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>4.2249999999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3629,6 +3683,9 @@
                 <c:pt idx="41">
                   <c:v>46265</c:v>
                 </c:pt>
+                <c:pt idx="42">
+                  <c:v>46272</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3763,6 +3820,9 @@
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>6.5</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>6.45</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3935,6 +3995,9 @@
                 <c:pt idx="41">
                   <c:v>46265</c:v>
                 </c:pt>
+                <c:pt idx="42">
+                  <c:v>46272</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4069,6 +4132,9 @@
                 </c:pt>
                 <c:pt idx="41">
                   <c:v>12.3</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>12.275</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6333,7 +6399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y44"/>
+  <dimension ref="A1:Y45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="8" bestFit="1" customWidth="1"/>
@@ -8669,6 +8735,56 @@
       </c>
       <c r="P44" s="11">
         <v>18.437999999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45" s="8">
+        <v>46265</v>
+      </c>
+      <c r="B45" s="8">
+        <v>46272</v>
+      </c>
+      <c r="C45" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E45" s="11">
+        <v>4.55</v>
+      </c>
+      <c r="F45" s="11">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="G45" s="11">
+        <v>4.2750000000000004</v>
+      </c>
+      <c r="H45" s="11">
+        <v>3.68</v>
+      </c>
+      <c r="I45" s="11">
+        <v>2.9</v>
+      </c>
+      <c r="J45" s="11">
+        <v>3.4</v>
+      </c>
+      <c r="K45" s="11">
+        <v>55</v>
+      </c>
+      <c r="L45" s="11">
+        <v>33</v>
+      </c>
+      <c r="M45" s="11">
+        <v>38.587000000000003</v>
+      </c>
+      <c r="N45" s="11">
+        <v>20.2</v>
+      </c>
+      <c r="O45" s="11">
+        <v>17.7</v>
+      </c>
+      <c r="P45" s="11">
+        <v>18.638000000000002</v>
       </c>
     </row>
   </sheetData>
@@ -9155,7 +9271,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54319F21-0FC0-45E2-9E0C-131772CB34B0}">
-  <dimension ref="A1:Y44"/>
+  <dimension ref="A1:Y45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
@@ -11139,6 +11255,47 @@
         <v>8</v>
       </c>
       <c r="M44" s="11">
+        <v>9.9670000000000005</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13">
+      <c r="A45" s="8">
+        <v>46265</v>
+      </c>
+      <c r="B45" s="8">
+        <v>46272</v>
+      </c>
+      <c r="C45" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E45" s="11">
+        <v>22</v>
+      </c>
+      <c r="F45" s="11">
+        <v>17.5</v>
+      </c>
+      <c r="G45" s="11">
+        <v>20.707999999999998</v>
+      </c>
+      <c r="H45" s="11">
+        <v>19</v>
+      </c>
+      <c r="I45" s="11">
+        <v>14</v>
+      </c>
+      <c r="J45" s="11">
+        <v>16.808</v>
+      </c>
+      <c r="K45" s="11">
+        <v>15</v>
+      </c>
+      <c r="L45" s="11">
+        <v>8</v>
+      </c>
+      <c r="M45" s="11">
         <v>9.9670000000000005</v>
       </c>
     </row>
@@ -11156,7 +11313,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873B53F4-91AF-4D49-84B3-FC7BC3C51C10}">
-  <dimension ref="A1:Y44"/>
+  <dimension ref="A1:Y45"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
@@ -13494,6 +13651,56 @@
       </c>
       <c r="P44" s="11">
         <v>12.3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45" s="8">
+        <v>46265</v>
+      </c>
+      <c r="B45" s="8">
+        <v>46272</v>
+      </c>
+      <c r="C45" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E45" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="F45" s="11">
+        <v>2.85</v>
+      </c>
+      <c r="G45" s="11">
+        <v>2.9649999999999999</v>
+      </c>
+      <c r="H45" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="I45" s="11">
+        <v>3.9</v>
+      </c>
+      <c r="J45" s="11">
+        <v>4.2249999999999996</v>
+      </c>
+      <c r="K45" s="11">
+        <v>7</v>
+      </c>
+      <c r="L45" s="11">
+        <v>6</v>
+      </c>
+      <c r="M45" s="11">
+        <v>6.45</v>
+      </c>
+      <c r="N45" s="11">
+        <v>13</v>
+      </c>
+      <c r="O45" s="11">
+        <v>12</v>
+      </c>
+      <c r="P45" s="11">
+        <v>12.275</v>
       </c>
     </row>
   </sheetData>
@@ -13782,7 +13989,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8A9E7BC-4FDA-42FF-94EB-B5FEB168C665}">
-  <dimension ref="A1:AJ23"/>
+  <dimension ref="A1:AJ24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="8" bestFit="1" customWidth="1"/>
@@ -15326,6 +15533,65 @@
         <v>164.97</v>
       </c>
       <c r="V23" s="11">
+        <v>177.47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22">
+      <c r="A24" s="8">
+        <v>46276</v>
+      </c>
+      <c r="B24" s="8">
+        <v>46276</v>
+      </c>
+      <c r="C24" s="9">
+        <v>0.4375</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E24" s="11">
+        <v>181.88</v>
+      </c>
+      <c r="F24" s="11">
+        <v>178.67</v>
+      </c>
+      <c r="G24" s="11">
+        <v>180.28</v>
+      </c>
+      <c r="H24" s="11">
+        <v>150.30000000000001</v>
+      </c>
+      <c r="I24" s="11">
+        <v>115.7</v>
+      </c>
+      <c r="J24" s="11">
+        <v>133</v>
+      </c>
+      <c r="K24" s="11">
+        <v>239.99</v>
+      </c>
+      <c r="L24" s="11">
+        <v>239.99</v>
+      </c>
+      <c r="M24" s="11">
+        <v>239.99</v>
+      </c>
+      <c r="Q24" s="11">
+        <v>390</v>
+      </c>
+      <c r="R24" s="11">
+        <v>390</v>
+      </c>
+      <c r="S24" s="11">
+        <v>390</v>
+      </c>
+      <c r="T24" s="11">
+        <v>189.97</v>
+      </c>
+      <c r="U24" s="11">
+        <v>164.97</v>
+      </c>
+      <c r="V24" s="11">
         <v>177.47</v>
       </c>
     </row>

--- a/data_lake/industry/TrendForce/NAND Flash.xlsx
+++ b/data_lake/industry/TrendForce/NAND Flash.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/industry/TrendForce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D666164E-F996-B140-9BFD-7B019481A16E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1558C940-DA82-2942-B675-A4F696665BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17280" yWindow="780" windowWidth="18720" windowHeight="20700" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17280" yWindow="780" windowWidth="18720" windowHeight="20700" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Flash" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="76">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -644,6 +644,9 @@
                 <c:pt idx="32">
                   <c:v>46272</c:v>
                 </c:pt>
+                <c:pt idx="33">
+                  <c:v>46279</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -751,6 +754,9 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>4.2750000000000004</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>4.3129999999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -896,6 +902,9 @@
                 <c:pt idx="32">
                   <c:v>46272</c:v>
                 </c:pt>
+                <c:pt idx="33">
+                  <c:v>46279</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1002,6 +1011,9 @@
                   <c:v>3.4449999999999998</c:v>
                 </c:pt>
                 <c:pt idx="32">
+                  <c:v>3.4</c:v>
+                </c:pt>
+                <c:pt idx="33">
                   <c:v>3.4</c:v>
                 </c:pt>
               </c:numCache>
@@ -1148,6 +1160,9 @@
                 <c:pt idx="32">
                   <c:v>46272</c:v>
                 </c:pt>
+                <c:pt idx="33">
+                  <c:v>46279</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1255,6 +1270,9 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>38.587000000000003</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>39.25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1400,6 +1418,9 @@
                 <c:pt idx="32">
                   <c:v>46272</c:v>
                 </c:pt>
+                <c:pt idx="33">
+                  <c:v>46279</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1507,6 +1528,9 @@
                 </c:pt>
                 <c:pt idx="32">
                   <c:v>18.638000000000002</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>18.937999999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1904,6 +1928,9 @@
                 <c:pt idx="42">
                   <c:v>46272</c:v>
                 </c:pt>
+                <c:pt idx="43">
+                  <c:v>46279</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2041,6 +2068,9 @@
                 </c:pt>
                 <c:pt idx="42">
                   <c:v>20.707999999999998</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>20.146000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2216,6 +2246,9 @@
                 <c:pt idx="42">
                   <c:v>46272</c:v>
                 </c:pt>
+                <c:pt idx="43">
+                  <c:v>46279</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2352,6 +2385,9 @@
                   <c:v>16.808</c:v>
                 </c:pt>
                 <c:pt idx="42">
+                  <c:v>16.808</c:v>
+                </c:pt>
+                <c:pt idx="43">
                   <c:v>16.808</c:v>
                 </c:pt>
               </c:numCache>
@@ -2528,6 +2564,9 @@
                 <c:pt idx="42">
                   <c:v>46272</c:v>
                 </c:pt>
+                <c:pt idx="43">
+                  <c:v>46279</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2664,6 +2703,9 @@
                   <c:v>9.9670000000000005</c:v>
                 </c:pt>
                 <c:pt idx="42">
+                  <c:v>9.9670000000000005</c:v>
+                </c:pt>
+                <c:pt idx="43">
                   <c:v>9.9670000000000005</c:v>
                 </c:pt>
               </c:numCache>
@@ -3062,6 +3104,9 @@
                 <c:pt idx="42">
                   <c:v>46272</c:v>
                 </c:pt>
+                <c:pt idx="43">
+                  <c:v>46279</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3198,6 +3243,9 @@
                   <c:v>2.9649999999999999</c:v>
                 </c:pt>
                 <c:pt idx="42">
+                  <c:v>2.9649999999999999</c:v>
+                </c:pt>
+                <c:pt idx="43">
                   <c:v>2.9649999999999999</c:v>
                 </c:pt>
               </c:numCache>
@@ -3374,6 +3422,9 @@
                 <c:pt idx="42">
                   <c:v>46272</c:v>
                 </c:pt>
+                <c:pt idx="43">
+                  <c:v>46279</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3511,6 +3562,9 @@
                 </c:pt>
                 <c:pt idx="42">
                   <c:v>4.2249999999999996</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>4.2300000000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3686,6 +3740,9 @@
                 <c:pt idx="42">
                   <c:v>46272</c:v>
                 </c:pt>
+                <c:pt idx="43">
+                  <c:v>46279</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3822,6 +3879,9 @@
                   <c:v>6.5</c:v>
                 </c:pt>
                 <c:pt idx="42">
+                  <c:v>6.45</c:v>
+                </c:pt>
+                <c:pt idx="43">
                   <c:v>6.45</c:v>
                 </c:pt>
               </c:numCache>
@@ -3998,6 +4058,9 @@
                 <c:pt idx="42">
                   <c:v>46272</c:v>
                 </c:pt>
+                <c:pt idx="43">
+                  <c:v>46279</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4135,6 +4198,9 @@
                 </c:pt>
                 <c:pt idx="42">
                   <c:v>12.275</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>12.29</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6399,7 +6465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y45"/>
+  <dimension ref="A1:Y46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="8" bestFit="1" customWidth="1"/>
@@ -8785,6 +8851,56 @@
       </c>
       <c r="P45" s="11">
         <v>18.638000000000002</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46" s="8">
+        <v>46272</v>
+      </c>
+      <c r="B46" s="8">
+        <v>46279</v>
+      </c>
+      <c r="C46" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E46" s="11">
+        <v>4.55</v>
+      </c>
+      <c r="F46" s="11">
+        <v>4.1500000000000004</v>
+      </c>
+      <c r="G46" s="11">
+        <v>4.3129999999999997</v>
+      </c>
+      <c r="H46" s="11">
+        <v>3.68</v>
+      </c>
+      <c r="I46" s="11">
+        <v>2.9</v>
+      </c>
+      <c r="J46" s="11">
+        <v>3.4</v>
+      </c>
+      <c r="K46" s="11">
+        <v>54</v>
+      </c>
+      <c r="L46" s="11">
+        <v>33</v>
+      </c>
+      <c r="M46" s="11">
+        <v>39.25</v>
+      </c>
+      <c r="N46" s="11">
+        <v>20.5</v>
+      </c>
+      <c r="O46" s="11">
+        <v>18</v>
+      </c>
+      <c r="P46" s="11">
+        <v>18.937999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -9271,7 +9387,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54319F21-0FC0-45E2-9E0C-131772CB34B0}">
-  <dimension ref="A1:Y45"/>
+  <dimension ref="A1:Y46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
@@ -11296,6 +11412,47 @@
         <v>8</v>
       </c>
       <c r="M45" s="11">
+        <v>9.9670000000000005</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13">
+      <c r="A46" s="8">
+        <v>46272</v>
+      </c>
+      <c r="B46" s="8">
+        <v>46279</v>
+      </c>
+      <c r="C46" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E46" s="11">
+        <v>22.5</v>
+      </c>
+      <c r="F46" s="11">
+        <v>17.5</v>
+      </c>
+      <c r="G46" s="11">
+        <v>20.146000000000001</v>
+      </c>
+      <c r="H46" s="11">
+        <v>19</v>
+      </c>
+      <c r="I46" s="11">
+        <v>14</v>
+      </c>
+      <c r="J46" s="11">
+        <v>16.808</v>
+      </c>
+      <c r="K46" s="11">
+        <v>15</v>
+      </c>
+      <c r="L46" s="11">
+        <v>8</v>
+      </c>
+      <c r="M46" s="11">
         <v>9.9670000000000005</v>
       </c>
     </row>
@@ -11313,7 +11470,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873B53F4-91AF-4D49-84B3-FC7BC3C51C10}">
-  <dimension ref="A1:Y45"/>
+  <dimension ref="A1:Y46"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
@@ -13701,6 +13858,56 @@
       </c>
       <c r="P45" s="11">
         <v>12.275</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46" s="8">
+        <v>46272</v>
+      </c>
+      <c r="B46" s="8">
+        <v>46279</v>
+      </c>
+      <c r="C46" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E46" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="F46" s="11">
+        <v>2.85</v>
+      </c>
+      <c r="G46" s="11">
+        <v>2.9649999999999999</v>
+      </c>
+      <c r="H46" s="11">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="I46" s="11">
+        <v>3.9</v>
+      </c>
+      <c r="J46" s="11">
+        <v>4.2300000000000004</v>
+      </c>
+      <c r="K46" s="11">
+        <v>7</v>
+      </c>
+      <c r="L46" s="11">
+        <v>6</v>
+      </c>
+      <c r="M46" s="11">
+        <v>6.45</v>
+      </c>
+      <c r="N46" s="11">
+        <v>13</v>
+      </c>
+      <c r="O46" s="11">
+        <v>12</v>
+      </c>
+      <c r="P46" s="11">
+        <v>12.29</v>
       </c>
     </row>
   </sheetData>
@@ -13989,7 +14196,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8A9E7BC-4FDA-42FF-94EB-B5FEB168C665}">
-  <dimension ref="A1:AJ24"/>
+  <dimension ref="A1:AJ25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.33203125" style="8" bestFit="1" customWidth="1"/>
@@ -15593,6 +15800,65 @@
       </c>
       <c r="V24" s="11">
         <v>177.47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22">
+      <c r="A25" s="8">
+        <v>46290</v>
+      </c>
+      <c r="B25" s="8">
+        <v>46290</v>
+      </c>
+      <c r="C25" s="9">
+        <v>0.54166666666666663</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E25" s="11">
+        <v>180.48</v>
+      </c>
+      <c r="F25" s="11">
+        <v>180.38</v>
+      </c>
+      <c r="G25" s="11">
+        <v>180.43</v>
+      </c>
+      <c r="H25" s="11">
+        <v>150.30000000000001</v>
+      </c>
+      <c r="I25" s="11">
+        <v>115.7</v>
+      </c>
+      <c r="J25" s="11">
+        <v>133</v>
+      </c>
+      <c r="K25" s="11">
+        <v>239.99</v>
+      </c>
+      <c r="L25" s="11">
+        <v>239.99</v>
+      </c>
+      <c r="M25" s="11">
+        <v>239.99</v>
+      </c>
+      <c r="Q25" s="11">
+        <v>390</v>
+      </c>
+      <c r="R25" s="11">
+        <v>390</v>
+      </c>
+      <c r="S25" s="11">
+        <v>390</v>
+      </c>
+      <c r="T25" s="11">
+        <v>189.97</v>
+      </c>
+      <c r="U25" s="11">
+        <v>189.97</v>
+      </c>
+      <c r="V25" s="11">
+        <v>189.97</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/industry/TrendForce/NAND Flash.xlsx
+++ b/data_lake/industry/TrendForce/NAND Flash.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/industry/TrendForce/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1558C940-DA82-2942-B675-A4F696665BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62C9238E-BB25-E746-8717-96186EED7A73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17280" yWindow="780" windowWidth="18720" windowHeight="20700" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Flash" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="76">
   <si>
     <t>Base Date</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -647,6 +647,9 @@
                 <c:pt idx="33">
                   <c:v>46279</c:v>
                 </c:pt>
+                <c:pt idx="34">
+                  <c:v>46286</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -757,6 +760,9 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>4.3129999999999997</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>4.3230000000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -905,6 +911,9 @@
                 <c:pt idx="33">
                   <c:v>46279</c:v>
                 </c:pt>
+                <c:pt idx="34">
+                  <c:v>46286</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1015,6 +1024,9 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>3.4</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>3.3580000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1163,6 +1175,9 @@
                 <c:pt idx="33">
                   <c:v>46279</c:v>
                 </c:pt>
+                <c:pt idx="34">
+                  <c:v>46286</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1273,6 +1288,9 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>39.25</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>39.912999999999997</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1421,6 +1439,9 @@
                 <c:pt idx="33">
                   <c:v>46279</c:v>
                 </c:pt>
+                <c:pt idx="34">
+                  <c:v>46286</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1531,6 +1552,9 @@
                 </c:pt>
                 <c:pt idx="33">
                   <c:v>18.937999999999999</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>19.033000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1931,6 +1955,9 @@
                 <c:pt idx="43">
                   <c:v>46279</c:v>
                 </c:pt>
+                <c:pt idx="44">
+                  <c:v>46286</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2071,6 +2098,9 @@
                 </c:pt>
                 <c:pt idx="43">
                   <c:v>20.146000000000001</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>20.082999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2249,6 +2279,9 @@
                 <c:pt idx="43">
                   <c:v>46279</c:v>
                 </c:pt>
+                <c:pt idx="44">
+                  <c:v>46286</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2388,6 +2421,9 @@
                   <c:v>16.808</c:v>
                 </c:pt>
                 <c:pt idx="43">
+                  <c:v>16.808</c:v>
+                </c:pt>
+                <c:pt idx="44">
                   <c:v>16.808</c:v>
                 </c:pt>
               </c:numCache>
@@ -2567,6 +2603,9 @@
                 <c:pt idx="43">
                   <c:v>46279</c:v>
                 </c:pt>
+                <c:pt idx="44">
+                  <c:v>46286</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2706,6 +2745,9 @@
                   <c:v>9.9670000000000005</c:v>
                 </c:pt>
                 <c:pt idx="43">
+                  <c:v>9.9670000000000005</c:v>
+                </c:pt>
+                <c:pt idx="44">
                   <c:v>9.9670000000000005</c:v>
                 </c:pt>
               </c:numCache>
@@ -3107,6 +3149,9 @@
                 <c:pt idx="43">
                   <c:v>46279</c:v>
                 </c:pt>
+                <c:pt idx="44">
+                  <c:v>46286</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3246,6 +3291,9 @@
                   <c:v>2.9649999999999999</c:v>
                 </c:pt>
                 <c:pt idx="43">
+                  <c:v>2.9649999999999999</c:v>
+                </c:pt>
+                <c:pt idx="44">
                   <c:v>2.9649999999999999</c:v>
                 </c:pt>
               </c:numCache>
@@ -3425,6 +3473,9 @@
                 <c:pt idx="43">
                   <c:v>46279</c:v>
                 </c:pt>
+                <c:pt idx="44">
+                  <c:v>46286</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3565,6 +3616,9 @@
                 </c:pt>
                 <c:pt idx="43">
                   <c:v>4.2300000000000004</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>4.1749999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3743,6 +3797,9 @@
                 <c:pt idx="43">
                   <c:v>46279</c:v>
                 </c:pt>
+                <c:pt idx="44">
+                  <c:v>46286</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3883,6 +3940,9 @@
                 </c:pt>
                 <c:pt idx="43">
                   <c:v>6.45</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>6.4249999999999998</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4061,6 +4121,9 @@
                 <c:pt idx="43">
                   <c:v>46279</c:v>
                 </c:pt>
+                <c:pt idx="44">
+                  <c:v>46286</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4200,6 +4263,9 @@
                   <c:v>12.275</c:v>
                 </c:pt>
                 <c:pt idx="43">
+                  <c:v>12.29</c:v>
+                </c:pt>
+                <c:pt idx="44">
                   <c:v>12.29</c:v>
                 </c:pt>
               </c:numCache>
@@ -6465,7 +6531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y46"/>
+  <dimension ref="A1:Y47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.83203125" style="8" bestFit="1" customWidth="1"/>
@@ -8901,6 +8967,56 @@
       </c>
       <c r="P46" s="11">
         <v>18.937999999999999</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47" s="8">
+        <v>46279</v>
+      </c>
+      <c r="B47" s="8">
+        <v>46286</v>
+      </c>
+      <c r="C47" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E47" s="11">
+        <v>4.55</v>
+      </c>
+      <c r="F47" s="11">
+        <v>4.16</v>
+      </c>
+      <c r="G47" s="11">
+        <v>4.3230000000000004</v>
+      </c>
+      <c r="H47" s="11">
+        <v>3.65</v>
+      </c>
+      <c r="I47" s="11">
+        <v>2.9</v>
+      </c>
+      <c r="J47" s="11">
+        <v>3.3580000000000001</v>
+      </c>
+      <c r="K47" s="11">
+        <v>53.5</v>
+      </c>
+      <c r="L47" s="11">
+        <v>34</v>
+      </c>
+      <c r="M47" s="11">
+        <v>39.912999999999997</v>
+      </c>
+      <c r="N47" s="11">
+        <v>21</v>
+      </c>
+      <c r="O47" s="11">
+        <v>18.5</v>
+      </c>
+      <c r="P47" s="11">
+        <v>19.033000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -9387,7 +9503,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54319F21-0FC0-45E2-9E0C-131772CB34B0}">
-  <dimension ref="A1:Y46"/>
+  <dimension ref="A1:Y47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
@@ -11453,6 +11569,47 @@
         <v>8</v>
       </c>
       <c r="M46" s="11">
+        <v>9.9670000000000005</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13">
+      <c r="A47" s="8">
+        <v>46279</v>
+      </c>
+      <c r="B47" s="8">
+        <v>46286</v>
+      </c>
+      <c r="C47" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E47" s="11">
+        <v>22</v>
+      </c>
+      <c r="F47" s="11">
+        <v>17.5</v>
+      </c>
+      <c r="G47" s="11">
+        <v>20.082999999999998</v>
+      </c>
+      <c r="H47" s="11">
+        <v>19</v>
+      </c>
+      <c r="I47" s="11">
+        <v>14</v>
+      </c>
+      <c r="J47" s="11">
+        <v>16.808</v>
+      </c>
+      <c r="K47" s="11">
+        <v>15</v>
+      </c>
+      <c r="L47" s="11">
+        <v>8</v>
+      </c>
+      <c r="M47" s="11">
         <v>9.9670000000000005</v>
       </c>
     </row>
@@ -11470,7 +11627,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{873B53F4-91AF-4D49-84B3-FC7BC3C51C10}">
-  <dimension ref="A1:Y46"/>
+  <dimension ref="A1:Y47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.1640625" style="8" bestFit="1" customWidth="1"/>
@@ -13910,6 +14067,56 @@
         <v>12.29</v>
       </c>
     </row>
+    <row r="47" spans="1:16">
+      <c r="A47" s="8">
+        <v>46279</v>
+      </c>
+      <c r="B47" s="8">
+        <v>46286</v>
+      </c>
+      <c r="C47" s="9">
+        <v>0.61111111111111105</v>
+      </c>
+      <c r="D47" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E47" s="11">
+        <v>3.2</v>
+      </c>
+      <c r="F47" s="11">
+        <v>2.85</v>
+      </c>
+      <c r="G47" s="11">
+        <v>2.9649999999999999</v>
+      </c>
+      <c r="H47" s="11">
+        <v>4.8</v>
+      </c>
+      <c r="I47" s="11">
+        <v>3.8</v>
+      </c>
+      <c r="J47" s="11">
+        <v>4.1749999999999998</v>
+      </c>
+      <c r="K47" s="11">
+        <v>7</v>
+      </c>
+      <c r="L47" s="11">
+        <v>6</v>
+      </c>
+      <c r="M47" s="11">
+        <v>6.4249999999999998</v>
+      </c>
+      <c r="N47" s="11">
+        <v>13</v>
+      </c>
+      <c r="O47" s="11">
+        <v>12</v>
+      </c>
+      <c r="P47" s="11">
+        <v>12.29</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:A2"/>
@@ -13924,7 +14131,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD3DFE18-E6A7-46E2-A20D-CA2E453C377B}">
-  <dimension ref="A1:Y5"/>
+  <dimension ref="A1:Y6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="11.33203125" style="21" bestFit="1" customWidth="1"/>
@@ -14180,6 +14387,47 @@
       </c>
       <c r="M5" s="22">
         <v>104.6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25">
+      <c r="A6" s="19">
+        <v>46239</v>
+      </c>
+      <c r="B6" s="19">
+        <v>46239</v>
+      </c>
+      <c r="C6" s="20">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="22">
+        <v>385</v>
+      </c>
+      <c r="F6" s="22">
+        <v>265</v>
+      </c>
+      <c r="G6" s="22">
+        <v>321</v>
+      </c>
+      <c r="H6" s="22">
+        <v>210</v>
+      </c>
+      <c r="I6" s="22">
+        <v>165</v>
+      </c>
+      <c r="J6" s="22">
+        <v>201.13</v>
+      </c>
+      <c r="K6" s="22">
+        <v>160</v>
+      </c>
+      <c r="L6" s="22">
+        <v>110</v>
+      </c>
+      <c r="M6" s="22">
+        <v>128.38</v>
       </c>
     </row>
   </sheetData>
